--- a/recruiter_forms/002_interview_request_form--recruiter_forms.xlsx
+++ b/recruiter_forms/002_interview_request_form--recruiter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'john_smith',_'value':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'John Smith', 'value': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Jane Doe', 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'bob_johnson',_'value':_'bob_johnson'}</t>
+          <t>bob_johnson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Bob Johnson', 'value': 'Bob Johnson'}</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Monday', 'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Tuesday', 'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Wednesday', 'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Thursday', 'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Friday', 'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Saturday', 'value': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Sunday', 'value': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'value': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'video',_'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'video', 'value': 'video'}</t>
+          <t>video</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'in_person',_'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'in_person', 'value': 'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
